--- a/AMD_Model.xlsx
+++ b/AMD_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648B94E8-5CA3-4863-A3AA-0E5836669584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395E51D5-179C-49DD-97C6-0E7E787A1815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="12435" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -5883,7 +5883,7 @@
     <t>11/5/25</t>
   </si>
   <si>
-    <t>12/30/25</t>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -21492,7 +21492,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="78">
-        <v>215.08</v>
+        <v>200.54</v>
       </c>
       <c r="D3" s="42" t="s">
         <v>1781</v>
@@ -21515,7 +21515,7 @@
       </c>
       <c r="C5" s="77">
         <f>C3*C4</f>
-        <v>349720.08</v>
+        <v>326078.03999999998</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="C8" s="77">
         <f>C5-C6+C7</f>
-        <v>345697.08</v>
+        <v>322055.03999999998</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="15">
@@ -23173,9 +23173,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3" twoDigitTextYear="1"/>
-  </ignoredErrors>
   <drawing r:id="rId10"/>
 </worksheet>
 </file>
@@ -23828,39 +23825,39 @@
       </c>
       <c r="CM4" s="69">
         <f t="shared" ref="CM4:CU4" si="6">CL4*(1+CM11)</f>
-        <v>20732.7078</v>
+        <v>21744.059400000002</v>
       </c>
       <c r="CN4" s="69">
         <f t="shared" si="6"/>
-        <v>25293.903515999998</v>
+        <v>26745.193062000002</v>
       </c>
       <c r="CO4" s="69">
         <f t="shared" si="6"/>
-        <v>30352.684219199997</v>
+        <v>32361.68360502</v>
       </c>
       <c r="CP4" s="69">
         <f t="shared" si="6"/>
-        <v>35512.640536463994</v>
+        <v>38186.786653923598</v>
       </c>
       <c r="CQ4" s="69">
         <f t="shared" si="6"/>
-        <v>40484.41021156896</v>
+        <v>43914.804652012135</v>
       </c>
       <c r="CR4" s="69">
         <f t="shared" si="6"/>
-        <v>45342.539436957239</v>
+        <v>49623.729256773709</v>
       </c>
       <c r="CS4" s="69">
         <f t="shared" si="6"/>
-        <v>49876.793380652969</v>
+        <v>55082.339475018824</v>
       </c>
       <c r="CT4" s="69">
         <f t="shared" si="6"/>
-        <v>53866.936851105209</v>
+        <v>60039.750027770518</v>
       </c>
       <c r="CU4" s="69">
         <f t="shared" si="6"/>
-        <v>57098.953062171524</v>
+        <v>64242.532529714459</v>
       </c>
     </row>
     <row r="5" spans="2:152">
@@ -23950,39 +23947,39 @@
       </c>
       <c r="CM5" s="69">
         <f t="shared" si="7"/>
-        <v>13954.222799999998</v>
+        <v>16058.430999999999</v>
       </c>
       <c r="CN5" s="69">
         <f t="shared" si="7"/>
-        <v>17442.778499999997</v>
+        <v>20073.03875</v>
       </c>
       <c r="CO5" s="69">
         <f t="shared" si="7"/>
-        <v>21629.045339999997</v>
+        <v>24890.568049999998</v>
       </c>
       <c r="CP5" s="69">
         <f t="shared" si="7"/>
-        <v>26387.435314799997</v>
+        <v>30366.493020999998</v>
       </c>
       <c r="CQ5" s="69">
         <f t="shared" si="7"/>
-        <v>31664.922377759995</v>
+        <v>36439.7916252</v>
       </c>
       <c r="CR5" s="69">
         <f t="shared" si="7"/>
-        <v>37364.608405756793</v>
+        <v>42998.954117736001</v>
       </c>
       <c r="CS5" s="69">
         <f t="shared" si="7"/>
-        <v>42969.299666620311</v>
+        <v>49448.7972353964</v>
       </c>
       <c r="CT5" s="69">
         <f t="shared" si="7"/>
-        <v>48125.615626614752</v>
+        <v>55382.652903643975</v>
       </c>
       <c r="CU5" s="69">
         <f t="shared" si="7"/>
-        <v>52938.177189276234</v>
+        <v>60920.91819400838</v>
       </c>
     </row>
     <row r="6" spans="2:152">
@@ -24214,39 +24211,39 @@
       </c>
       <c r="CM7" s="70">
         <f t="shared" ref="CM7:CU7" si="9">SUM(CM5:CM6)</f>
-        <v>17720.605799999998</v>
+        <v>19824.813999999998</v>
       </c>
       <c r="CN7" s="70">
         <f t="shared" si="9"/>
-        <v>21811.782779999994</v>
+        <v>24442.043030000001</v>
       </c>
       <c r="CO7" s="70">
         <f t="shared" si="9"/>
-        <v>26653.400261999996</v>
+        <v>29914.922971999997</v>
       </c>
       <c r="CP7" s="70">
         <f t="shared" si="9"/>
-        <v>32115.199925879995</v>
+        <v>36094.25763208</v>
       </c>
       <c r="CQ7" s="70">
         <f t="shared" si="9"/>
-        <v>38137.296388280389</v>
+        <v>42912.165635720397</v>
       </c>
       <c r="CR7" s="70">
         <f t="shared" si="9"/>
-        <v>44613.667297539636</v>
+        <v>50248.013009518851</v>
       </c>
       <c r="CS7" s="70">
         <f t="shared" si="9"/>
-        <v>50798.283269745785</v>
+        <v>57277.780838521874</v>
       </c>
       <c r="CT7" s="70">
         <f t="shared" si="9"/>
-        <v>56424.338245927756</v>
+        <v>63681.37552295698</v>
       </c>
       <c r="CU7" s="70">
         <f t="shared" si="9"/>
-        <v>61568.84871336176</v>
+        <v>69551.589718093906</v>
       </c>
       <c r="CV7" s="55"/>
       <c r="CW7" s="55"/>
@@ -24530,39 +24527,39 @@
       </c>
       <c r="CM9" s="70">
         <f t="shared" ref="CM9:CU9" si="12">CM4+CM7+CM8</f>
-        <v>41900.046599999994</v>
+        <v>45015.606399999997</v>
       </c>
       <c r="CN9" s="70">
         <f t="shared" si="12"/>
-        <v>50621.353955999992</v>
+        <v>54702.903752000006</v>
       </c>
       <c r="CO9" s="70">
         <f t="shared" si="12"/>
-        <v>60592.065494399991</v>
+        <v>65862.587590219991</v>
       </c>
       <c r="CP9" s="70">
         <f t="shared" si="12"/>
-        <v>71285.541095807988</v>
+        <v>77938.744919467601</v>
       </c>
       <c r="CQ9" s="70">
         <f t="shared" si="12"/>
-        <v>82352.561245982622</v>
+        <v>90557.824933865806</v>
       </c>
       <c r="CR9" s="70">
         <f t="shared" si="12"/>
-        <v>93761.67847355282</v>
+        <v>103677.21400534852</v>
       </c>
       <c r="CS9" s="70">
         <f t="shared" si="12"/>
-        <v>104556.65782423582</v>
+        <v>116241.70148737777</v>
       </c>
       <c r="CT9" s="70">
         <f t="shared" si="12"/>
-        <v>114250.48789434678</v>
+        <v>127680.33834804132</v>
       </c>
       <c r="CU9" s="70">
         <f t="shared" si="12"/>
-        <v>122706.19882879336</v>
+        <v>137832.51930106847</v>
       </c>
       <c r="CV9" s="55"/>
       <c r="CW9" s="55"/>
@@ -24716,31 +24713,31 @@
         <v>0.34</v>
       </c>
       <c r="CM11" s="71">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="CN11" s="71">
         <v>0.23</v>
       </c>
-      <c r="CN11" s="71">
-        <v>0.22</v>
-      </c>
       <c r="CO11" s="71">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="CP11" s="71">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="CQ11" s="71">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="CR11" s="71">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="CS11" s="71">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="CT11" s="71">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="CU11" s="71">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="12" spans="2:152">
@@ -24839,7 +24836,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="CM12" s="71">
-        <v>0.26</v>
+        <v>0.45</v>
       </c>
       <c r="CN12" s="71">
         <v>0.25</v>
@@ -25215,39 +25212,39 @@
       </c>
       <c r="CM15" s="79">
         <f t="shared" ref="CM15:CU15" si="17">CM9/CL9-1</f>
-        <v>0.21443637461871368</v>
+        <v>0.30473816317137392</v>
       </c>
       <c r="CN15" s="79">
         <f t="shared" si="17"/>
-        <v>0.2081455287928009</v>
+        <v>0.21519864168707525</v>
       </c>
       <c r="CO15" s="79">
         <f t="shared" si="17"/>
-        <v>0.19696651233521978</v>
+        <v>0.20400532828775053</v>
       </c>
       <c r="CP15" s="79">
         <f t="shared" si="17"/>
-        <v>0.17648310078481</v>
+        <v>0.18335382454728832</v>
       </c>
       <c r="CQ15" s="79">
         <f t="shared" si="17"/>
-        <v>0.15524915684234664</v>
+        <v>0.16191022869866867</v>
       </c>
       <c r="CR15" s="79">
         <f t="shared" si="17"/>
-        <v>0.13853991976632996</v>
+        <v>0.14487305852436028</v>
       </c>
       <c r="CS15" s="79">
         <f t="shared" si="17"/>
-        <v>0.11513210435677013</v>
+        <v>0.12118851381732787</v>
       </c>
       <c r="CT15" s="79">
         <f t="shared" si="17"/>
-        <v>9.2713656612921636E-2</v>
+        <v>9.8403900788613496E-2</v>
       </c>
       <c r="CU15" s="79">
         <f t="shared" si="17"/>
-        <v>7.4010282934336535E-2</v>
+        <v>7.9512484728490707E-2</v>
       </c>
       <c r="CV15" s="55"/>
       <c r="CW15" s="55"/>
@@ -25427,39 +25424,39 @@
       </c>
       <c r="CM17" s="71">
         <f t="shared" si="19"/>
-        <v>0.49481347832200268</v>
+        <v>0.48303379958467035</v>
       </c>
       <c r="CN17" s="71">
         <f t="shared" si="19"/>
-        <v>0.49966864849141379</v>
+        <v>0.48891724620783344</v>
       </c>
       <c r="CO17" s="71">
         <f t="shared" si="19"/>
-        <v>0.50093496518954672</v>
+        <v>0.49135153641952295</v>
       </c>
       <c r="CP17" s="71">
         <f t="shared" si="19"/>
-        <v>0.49817452446261012</v>
+        <v>0.48995896320092364</v>
       </c>
       <c r="CQ17" s="71">
         <f t="shared" si="19"/>
-        <v>0.49159867767371834</v>
+        <v>0.48493661021654427</v>
       </c>
       <c r="CR17" s="71">
         <f t="shared" si="19"/>
-        <v>0.48359351256437805</v>
+        <v>0.47863679336728426</v>
       </c>
       <c r="CS17" s="71">
         <f t="shared" si="19"/>
-        <v>0.47703125194091395</v>
+        <v>0.47386040268001411</v>
       </c>
       <c r="CT17" s="71">
         <f t="shared" si="19"/>
-        <v>0.47148102247859719</v>
+        <v>0.4702348913276635</v>
       </c>
       <c r="CU17" s="71">
         <f t="shared" si="19"/>
-        <v>0.46533063208843439</v>
+        <v>0.46609125956254976</v>
       </c>
     </row>
     <row r="18" spans="2:151">
@@ -25575,39 +25572,39 @@
       </c>
       <c r="CM18" s="71">
         <f t="shared" si="21"/>
-        <v>0.3330359732821872</v>
+        <v>0.35673030498151859</v>
       </c>
       <c r="CN18" s="71">
         <f t="shared" si="21"/>
-        <v>0.34457352751096376</v>
+        <v>0.36694649412036201</v>
       </c>
       <c r="CO18" s="71">
         <f t="shared" si="21"/>
-        <v>0.35696167746582241</v>
+        <v>0.37791664373806089</v>
       </c>
       <c r="CP18" s="71">
         <f t="shared" si="21"/>
-        <v>0.37016532257691925</v>
+        <v>0.38961999006241416</v>
       </c>
       <c r="CQ18" s="71">
         <f t="shared" si="21"/>
-        <v>0.38450440276142223</v>
+        <v>0.40239252269819759</v>
       </c>
       <c r="CR18" s="71">
         <f t="shared" si="21"/>
-        <v>0.39850618092653023</v>
+        <v>0.41473871120338712</v>
       </c>
       <c r="CS18" s="71">
         <f t="shared" si="21"/>
-        <v>0.41096665253831588</v>
+        <v>0.42539636466664982</v>
       </c>
       <c r="CT18" s="71">
         <f t="shared" si="21"/>
-        <v>0.42122897252849328</v>
+        <v>0.43376022980670281</v>
       </c>
       <c r="CU18" s="71">
         <f t="shared" si="21"/>
-        <v>0.43142219133638532</v>
+        <v>0.44199234333763004</v>
       </c>
     </row>
     <row r="19" spans="2:151">
@@ -25723,39 +25720,39 @@
       </c>
       <c r="CM19" s="71">
         <f t="shared" si="23"/>
-        <v>8.9889709096409462E-2</v>
+        <v>8.3668383061035467E-2</v>
       </c>
       <c r="CN19" s="71">
         <f t="shared" si="23"/>
-        <v>8.630753503348669E-2</v>
+        <v>7.9867867706022153E-2</v>
       </c>
       <c r="CO19" s="71">
         <f t="shared" si="23"/>
-        <v>8.2921004276778731E-2</v>
+        <v>7.6285416437936474E-2</v>
       </c>
       <c r="CP19" s="71">
         <f t="shared" si="23"/>
-        <v>8.0349598572617489E-2</v>
+        <v>7.3490593375584543E-2</v>
       </c>
       <c r="CQ19" s="71">
         <f t="shared" si="23"/>
-        <v>7.8593475571303348E-2</v>
+        <v>7.1472277688285457E-2</v>
       </c>
       <c r="CR19" s="71">
         <f t="shared" si="23"/>
-        <v>7.7313663852845535E-2</v>
+        <v>6.9919499297202189E-2</v>
       </c>
       <c r="CS19" s="71">
         <f t="shared" si="23"/>
-        <v>7.4877906065879879E-2</v>
+        <v>6.7350903358684863E-2</v>
       </c>
       <c r="CT19" s="71">
         <f t="shared" si="23"/>
-        <v>7.2636211645653995E-2</v>
+        <v>6.4996088878552918E-2</v>
       </c>
       <c r="CU19" s="71">
         <f t="shared" si="23"/>
-        <v>7.0336067830831628E-2</v>
+        <v>6.2617091872444783E-2</v>
       </c>
     </row>
     <row r="20" spans="2:151">
@@ -25871,39 +25868,39 @@
       </c>
       <c r="CM20" s="71">
         <f t="shared" si="25"/>
-        <v>8.2260839299400687E-2</v>
+        <v>7.6567512372775676E-2</v>
       </c>
       <c r="CN20" s="71">
         <f t="shared" si="25"/>
-        <v>6.9450288964135826E-2</v>
+        <v>6.4268391965782296E-2</v>
       </c>
       <c r="CO20" s="71">
         <f t="shared" si="25"/>
-        <v>5.918235306785212E-2</v>
+        <v>5.4446403404479753E-2</v>
       </c>
       <c r="CP20" s="71">
         <f t="shared" si="25"/>
-        <v>5.1310554387853195E-2</v>
+        <v>4.6930453361077623E-2</v>
       </c>
       <c r="CQ20" s="71">
         <f t="shared" si="25"/>
-        <v>4.5303443993556194E-2</v>
+        <v>4.1198589396972775E-2</v>
       </c>
       <c r="CR20" s="71">
         <f t="shared" si="25"/>
-        <v>4.0586642656246265E-2</v>
+        <v>3.6704996132126279E-2</v>
       </c>
       <c r="CS20" s="71">
         <f t="shared" si="25"/>
-        <v>3.7124189454890259E-2</v>
+        <v>3.3392329294651205E-2</v>
       </c>
       <c r="CT20" s="71">
         <f t="shared" si="25"/>
-        <v>3.465379334725547E-2</v>
+        <v>3.1008789987080596E-2</v>
       </c>
       <c r="CU20" s="71">
         <f t="shared" si="25"/>
-        <v>3.2911108744348626E-2</v>
+        <v>2.9299305227375155E-2</v>
       </c>
     </row>
     <row r="22" spans="2:151" s="2" customFormat="1" ht="15">
@@ -26200,39 +26197,39 @@
       </c>
       <c r="CM22" s="70">
         <f t="shared" ref="CM22:CU22" si="33">CM9</f>
-        <v>41900.046599999994</v>
+        <v>45015.606399999997</v>
       </c>
       <c r="CN22" s="70">
         <f t="shared" si="33"/>
-        <v>50621.353955999992</v>
+        <v>54702.903752000006</v>
       </c>
       <c r="CO22" s="70">
         <f t="shared" si="33"/>
-        <v>60592.065494399991</v>
+        <v>65862.587590219991</v>
       </c>
       <c r="CP22" s="70">
         <f t="shared" si="33"/>
-        <v>71285.541095807988</v>
+        <v>77938.744919467601</v>
       </c>
       <c r="CQ22" s="70">
         <f t="shared" si="33"/>
-        <v>82352.561245982622</v>
+        <v>90557.824933865806</v>
       </c>
       <c r="CR22" s="70">
         <f t="shared" si="33"/>
-        <v>93761.67847355282</v>
+        <v>103677.21400534852</v>
       </c>
       <c r="CS22" s="70">
         <f t="shared" si="33"/>
-        <v>104556.65782423582</v>
+        <v>116241.70148737777</v>
       </c>
       <c r="CT22" s="70">
         <f t="shared" si="33"/>
-        <v>114250.48789434678</v>
+        <v>127680.33834804132</v>
       </c>
       <c r="CU22" s="70">
         <f t="shared" si="33"/>
-        <v>122706.19882879336</v>
+        <v>137832.51930106847</v>
       </c>
       <c r="CV22" s="55"/>
       <c r="CW22" s="55"/>
@@ -26551,39 +26548,39 @@
       </c>
       <c r="CM23" s="69">
         <f t="shared" ref="CM23:CU23" si="44">CM22*(1-CM40)</f>
-        <v>20531.022833999996</v>
+        <v>22057.647136</v>
       </c>
       <c r="CN23" s="69">
         <f t="shared" si="44"/>
-        <v>24298.249898879996</v>
+        <v>26257.393800960002</v>
       </c>
       <c r="CO23" s="69">
         <f t="shared" si="44"/>
-        <v>28781.231109839995</v>
+        <v>31284.729105354494</v>
       </c>
       <c r="CP23" s="69">
         <f t="shared" si="44"/>
-        <v>33504.204315029754</v>
+        <v>36631.210112149769</v>
       </c>
       <c r="CQ23" s="69">
         <f t="shared" si="44"/>
-        <v>38293.940979381914</v>
+        <v>42109.388594247597</v>
       </c>
       <c r="CR23" s="69">
         <f t="shared" si="44"/>
-        <v>43130.372097834297</v>
+        <v>47691.518442460314</v>
       </c>
       <c r="CS23" s="69">
         <f t="shared" si="44"/>
-        <v>47573.279310027297</v>
+        <v>52889.974176756878</v>
       </c>
       <c r="CT23" s="69">
         <f t="shared" si="44"/>
-        <v>51412.719552456045</v>
+        <v>57456.152256618589</v>
       </c>
       <c r="CU23" s="69">
         <f t="shared" si="44"/>
-        <v>55217.789472957011</v>
+        <v>62024.633685480811</v>
       </c>
     </row>
     <row r="24" spans="2:151">
@@ -26907,39 +26904,39 @@
       </c>
       <c r="CM24" s="69">
         <f t="shared" ref="CM24:CU24" si="47">CM22-CM23</f>
-        <v>21369.023765999998</v>
+        <v>22957.959263999997</v>
       </c>
       <c r="CN24" s="69">
         <f t="shared" si="47"/>
-        <v>26323.104057119996</v>
+        <v>28445.509951040003</v>
       </c>
       <c r="CO24" s="69">
         <f t="shared" si="47"/>
-        <v>31810.834384559996</v>
+        <v>34577.858484865501</v>
       </c>
       <c r="CP24" s="69">
         <f t="shared" si="47"/>
-        <v>37781.336780778234</v>
+        <v>41307.534807317832</v>
       </c>
       <c r="CQ24" s="69">
         <f t="shared" si="47"/>
-        <v>44058.620266600708</v>
+        <v>48448.436339618209</v>
       </c>
       <c r="CR24" s="69">
         <f t="shared" si="47"/>
-        <v>50631.306375718523</v>
+        <v>55985.695562888206</v>
       </c>
       <c r="CS24" s="69">
         <f t="shared" si="47"/>
-        <v>56983.378514208525</v>
+        <v>63351.727310620889</v>
       </c>
       <c r="CT24" s="69">
         <f t="shared" si="47"/>
-        <v>62837.768341890733</v>
+        <v>70224.186091422729</v>
       </c>
       <c r="CU24" s="69">
         <f t="shared" si="47"/>
-        <v>67488.409355836353</v>
+        <v>75807.885615587671</v>
       </c>
     </row>
     <row r="25" spans="2:151">
@@ -27206,39 +27203,39 @@
       </c>
       <c r="CM25" s="69">
         <f t="shared" ref="CM25:CU25" si="48">CM22*CM41</f>
-        <v>9637.0107179999995</v>
+        <v>10353.589472</v>
       </c>
       <c r="CN25" s="69">
         <f t="shared" si="48"/>
-        <v>11389.804640099999</v>
+        <v>12308.153344200002</v>
       </c>
       <c r="CO25" s="69">
         <f t="shared" si="48"/>
-        <v>13330.254408767998</v>
+        <v>14489.769269848399</v>
       </c>
       <c r="CP25" s="69">
         <f t="shared" si="48"/>
-        <v>15326.391335598717</v>
+        <v>16756.830157685534</v>
       </c>
       <c r="CQ25" s="69">
         <f t="shared" si="48"/>
-        <v>17294.03786165635</v>
+        <v>19017.143236111817</v>
       </c>
       <c r="CR25" s="69">
         <f t="shared" si="48"/>
-        <v>19221.144087078326</v>
+        <v>21253.828871096444</v>
       </c>
       <c r="CS25" s="69">
         <f t="shared" si="48"/>
-        <v>20911.331564847165</v>
+        <v>23248.340297475555</v>
       </c>
       <c r="CT25" s="69">
         <f t="shared" si="48"/>
-        <v>22278.845139397621</v>
+        <v>24897.665977868059</v>
       </c>
       <c r="CU25" s="69">
         <f t="shared" si="48"/>
-        <v>23314.177777470741</v>
+        <v>26188.17866720301</v>
       </c>
     </row>
     <row r="26" spans="2:151">
@@ -27505,39 +27502,39 @@
       </c>
       <c r="CM26" s="69">
         <f t="shared" ref="CM26:CU26" si="49">CM22*CM42</f>
-        <v>4818.5053589999998</v>
+        <v>5176.7947359999998</v>
       </c>
       <c r="CN26" s="69">
         <f t="shared" si="49"/>
-        <v>5568.3489351599992</v>
+        <v>6017.3194127200004</v>
       </c>
       <c r="CO26" s="69">
         <f t="shared" si="49"/>
-        <v>6362.1668769119988</v>
+        <v>6915.5716969730993</v>
       </c>
       <c r="CP26" s="69">
         <f t="shared" si="49"/>
-        <v>7128.5541095807994</v>
+        <v>7793.8744919467608</v>
       </c>
       <c r="CQ26" s="69">
         <f t="shared" si="49"/>
-        <v>8029.3747214833056</v>
+        <v>8829.3879310519169</v>
       </c>
       <c r="CR26" s="69">
         <f t="shared" si="49"/>
-        <v>8907.3594549875179</v>
+        <v>9849.3353305081091</v>
       </c>
       <c r="CS26" s="69">
         <f t="shared" si="49"/>
-        <v>9671.4908487418143</v>
+        <v>10752.357387582444</v>
       </c>
       <c r="CT26" s="69">
         <f t="shared" si="49"/>
-        <v>10282.543910491209</v>
+        <v>11491.230451323718</v>
       </c>
       <c r="CU26" s="69">
         <f t="shared" si="49"/>
-        <v>11043.557894591402</v>
+        <v>12404.926737096162</v>
       </c>
     </row>
     <row r="27" spans="2:151">
@@ -28127,39 +28124,39 @@
       </c>
       <c r="CM28" s="69">
         <f t="shared" ref="CM28:CU28" si="52">SUM(CM25:CM27)</f>
-        <v>15715.516077</v>
+        <v>16790.384207999999</v>
       </c>
       <c r="CN28" s="69">
         <f t="shared" si="52"/>
-        <v>18281.153575259999</v>
+        <v>19648.472756920004</v>
       </c>
       <c r="CO28" s="69">
         <f t="shared" si="52"/>
-        <v>21081.571285679998</v>
+        <v>22794.4909668215</v>
       </c>
       <c r="CP28" s="69">
         <f t="shared" si="52"/>
-        <v>23913.552945179516</v>
+        <v>26009.312149632293</v>
       </c>
       <c r="CQ28" s="69">
         <f t="shared" si="52"/>
-        <v>26854.950458139658</v>
+        <v>29378.069042163734</v>
       </c>
       <c r="CR28" s="69">
         <f t="shared" si="52"/>
-        <v>29736.618310815848</v>
+        <v>32711.278970354553</v>
       </c>
       <c r="CS28" s="69">
         <f t="shared" si="52"/>
-        <v>32271.342920776478</v>
+        <v>35689.218192245498</v>
       </c>
       <c r="CT28" s="69">
         <f t="shared" si="52"/>
-        <v>34334.335582435706</v>
+        <v>38161.842961738657</v>
       </c>
       <c r="CU28" s="69">
         <f t="shared" si="52"/>
-        <v>36219.329531236363</v>
+        <v>40454.699263473391</v>
       </c>
     </row>
     <row r="29" spans="2:151">
@@ -28484,39 +28481,39 @@
       </c>
       <c r="CM29" s="69">
         <f t="shared" ref="CM29:CU29" si="55">CM24-CM28</f>
-        <v>5653.5076889999982</v>
+        <v>6167.5750559999979</v>
       </c>
       <c r="CN29" s="69">
         <f t="shared" si="55"/>
-        <v>8041.9504818599962</v>
+        <v>8797.0371941199992</v>
       </c>
       <c r="CO29" s="69">
         <f t="shared" si="55"/>
-        <v>10729.263098879997</v>
+        <v>11783.367518044</v>
       </c>
       <c r="CP29" s="69">
         <f t="shared" si="55"/>
-        <v>13867.783835598719</v>
+        <v>15298.222657685539</v>
       </c>
       <c r="CQ29" s="69">
         <f t="shared" si="55"/>
-        <v>17203.669808461051</v>
+        <v>19070.367297454475</v>
       </c>
       <c r="CR29" s="69">
         <f t="shared" si="55"/>
-        <v>20894.688064902675</v>
+        <v>23274.416592533653</v>
       </c>
       <c r="CS29" s="69">
         <f t="shared" si="55"/>
-        <v>24712.035593432047</v>
+        <v>27662.50911837539</v>
       </c>
       <c r="CT29" s="69">
         <f t="shared" si="55"/>
-        <v>28503.432759455027</v>
+        <v>32062.343129684072</v>
       </c>
       <c r="CU29" s="69">
         <f t="shared" si="55"/>
-        <v>31269.07982459999</v>
+        <v>35353.18635211428</v>
       </c>
     </row>
     <row r="30" spans="2:151">
@@ -28779,43 +28776,43 @@
       </c>
       <c r="CL30" s="69">
         <f t="shared" ref="CL30:CU30" si="56">CK47*$CU$49</f>
-        <v>444.97249999999997</v>
+        <v>492.31</v>
       </c>
       <c r="CM30" s="69">
         <f t="shared" si="56"/>
-        <v>851.72636484999998</v>
+        <v>948.18173385</v>
       </c>
       <c r="CN30" s="69">
         <f t="shared" si="56"/>
-        <v>1539.6548660446374</v>
+        <v>1780.7252782624498</v>
       </c>
       <c r="CO30" s="69">
         <f t="shared" si="56"/>
-        <v>2530.3928590179762</v>
+        <v>2990.821305103002</v>
       </c>
       <c r="CP30" s="69">
         <f t="shared" si="56"/>
-        <v>3901.4412850646272</v>
+        <v>4680.9885064710188</v>
       </c>
       <c r="CQ30" s="69">
         <f t="shared" si="56"/>
-        <v>5738.7791625412174</v>
+        <v>6966.6102636505293</v>
       </c>
       <c r="CR30" s="69">
         <f t="shared" si="56"/>
-        <v>8111.0283861428516</v>
+        <v>9945.2404966409431</v>
       </c>
       <c r="CS30" s="69">
         <f t="shared" si="56"/>
-        <v>11110.219467180959</v>
+        <v>13745.569267642517</v>
       </c>
       <c r="CT30" s="69">
         <f t="shared" si="56"/>
-        <v>14814.240640448343</v>
+        <v>18482.653435002965</v>
       </c>
       <c r="CU30" s="69">
         <f t="shared" si="56"/>
-        <v>19293.288069998351</v>
+        <v>24265.001042003161</v>
       </c>
     </row>
     <row r="31" spans="2:151">
@@ -29425,43 +29422,43 @@
       </c>
       <c r="CL32" s="69">
         <f>CL29+CL30</f>
-        <v>3643.9315999999999</v>
+        <v>3691.2691</v>
       </c>
       <c r="CM32" s="69">
         <f t="shared" ref="CM32:CU32" si="59">CM29+SUM(CM30:CM31)</f>
-        <v>6505.2340538499984</v>
+        <v>7115.7567898499983</v>
       </c>
       <c r="CN32" s="69">
         <f t="shared" si="59"/>
-        <v>9581.6053479046332</v>
+        <v>10577.762472382448</v>
       </c>
       <c r="CO32" s="69">
         <f t="shared" si="59"/>
-        <v>13259.655957897974</v>
+        <v>14774.188823147002</v>
       </c>
       <c r="CP32" s="69">
         <f t="shared" si="59"/>
-        <v>17769.225120663345</v>
+        <v>19979.211164156557</v>
       </c>
       <c r="CQ32" s="69">
         <f t="shared" si="59"/>
-        <v>22942.448971002268</v>
+        <v>26036.977561105006</v>
       </c>
       <c r="CR32" s="69">
         <f t="shared" si="59"/>
-        <v>29005.716451045526</v>
+        <v>33219.657089174594</v>
       </c>
       <c r="CS32" s="69">
         <f t="shared" si="59"/>
-        <v>35822.25506061301</v>
+        <v>41408.078386017907</v>
       </c>
       <c r="CT32" s="69">
         <f t="shared" si="59"/>
-        <v>43317.673399903368</v>
+        <v>50544.996564687041</v>
       </c>
       <c r="CU32" s="69">
         <f t="shared" si="59"/>
-        <v>50562.367894598341</v>
+        <v>59618.187394117442</v>
       </c>
     </row>
     <row r="33" spans="2:151">
@@ -29724,43 +29721,43 @@
       </c>
       <c r="CL33" s="69">
         <f>CL32*CL44</f>
-        <v>182.19658000000001</v>
+        <v>184.563455</v>
       </c>
       <c r="CM33" s="69">
         <f t="shared" ref="CM33:CU33" si="60">CM32*CM44</f>
-        <v>650.52340538499993</v>
+        <v>711.57567898499985</v>
       </c>
       <c r="CN33" s="69">
         <f t="shared" si="60"/>
-        <v>1149.792641748556</v>
+        <v>1269.3314966858939</v>
       </c>
       <c r="CO33" s="69">
         <f t="shared" si="60"/>
-        <v>1591.1587149477568</v>
+        <v>1772.9026587776402</v>
       </c>
       <c r="CP33" s="69">
         <f t="shared" si="60"/>
-        <v>2132.3070144796011</v>
+        <v>2397.5053396987869</v>
       </c>
       <c r="CQ33" s="69">
         <f t="shared" si="60"/>
-        <v>2753.0938765202723</v>
+        <v>3124.4373073326005</v>
       </c>
       <c r="CR33" s="69">
         <f t="shared" si="60"/>
-        <v>3480.685974125463</v>
+        <v>3986.3588507009513</v>
       </c>
       <c r="CS33" s="69">
         <f t="shared" si="60"/>
-        <v>4298.6706072735615</v>
+        <v>4968.9694063221486</v>
       </c>
       <c r="CT33" s="69">
         <f t="shared" si="60"/>
-        <v>5198.1208079884036</v>
+        <v>6065.3995877624448</v>
       </c>
       <c r="CU33" s="69">
         <f t="shared" si="60"/>
-        <v>6067.4841473518009</v>
+        <v>7154.1824872940924</v>
       </c>
     </row>
     <row r="34" spans="2:151">
@@ -30664,243 +30661,243 @@
       </c>
       <c r="CL36" s="70">
         <f>CL32-CL33</f>
-        <v>3461.7350200000001</v>
+        <v>3506.705645</v>
       </c>
       <c r="CM36" s="70">
         <f t="shared" ref="CM36:CU36" si="63">CM32-CM33</f>
-        <v>5854.7106484649985</v>
+        <v>6404.1811108649981</v>
       </c>
       <c r="CN36" s="70">
         <f t="shared" si="63"/>
-        <v>8431.8127061560772</v>
+        <v>9308.430975696554</v>
       </c>
       <c r="CO36" s="70">
         <f t="shared" si="63"/>
-        <v>11668.497242950218</v>
+        <v>13001.286164369361</v>
       </c>
       <c r="CP36" s="70">
         <f t="shared" si="63"/>
-        <v>15636.918106183744</v>
+        <v>17581.705824457771</v>
       </c>
       <c r="CQ36" s="70">
         <f t="shared" si="63"/>
-        <v>20189.355094481994</v>
+        <v>22912.540253772408</v>
       </c>
       <c r="CR36" s="70">
         <f t="shared" si="63"/>
-        <v>25525.030476920063</v>
+        <v>29233.298238473642</v>
       </c>
       <c r="CS36" s="70">
         <f t="shared" si="63"/>
-        <v>31523.584453339448</v>
+        <v>36439.10897969576</v>
       </c>
       <c r="CT36" s="70">
         <f t="shared" si="63"/>
-        <v>38119.552591914966</v>
+        <v>44479.596976924593</v>
       </c>
       <c r="CU36" s="70">
         <f t="shared" si="63"/>
-        <v>44494.883747246538</v>
+        <v>52464.004906823349</v>
       </c>
       <c r="CV36" s="70">
         <f t="shared" ref="CV36:EA36" si="64">CU36*(1+$CU$50)</f>
-        <v>45162.307003455229</v>
+        <v>53250.964980425691</v>
       </c>
       <c r="CW36" s="70">
         <f t="shared" si="64"/>
-        <v>45839.741608507051</v>
+        <v>54049.729455132074</v>
       </c>
       <c r="CX36" s="70">
         <f t="shared" si="64"/>
-        <v>46527.337732634653</v>
+        <v>54860.475396959053</v>
       </c>
       <c r="CY36" s="70">
         <f t="shared" si="64"/>
-        <v>47225.247798624165</v>
+        <v>55683.382527913433</v>
       </c>
       <c r="CZ36" s="70">
         <f t="shared" si="64"/>
-        <v>47933.626515603522</v>
+        <v>56518.633265832126</v>
       </c>
       <c r="DA36" s="70">
         <f t="shared" si="64"/>
-        <v>48652.630913337569</v>
+        <v>57366.412764819601</v>
       </c>
       <c r="DB36" s="70">
         <f t="shared" si="64"/>
-        <v>49382.420377037626</v>
+        <v>58226.908956291889</v>
       </c>
       <c r="DC36" s="70">
         <f t="shared" si="64"/>
-        <v>50123.156682693188</v>
+        <v>59100.312590636262</v>
       </c>
       <c r="DD36" s="70">
         <f t="shared" si="64"/>
-        <v>50875.004032933582</v>
+        <v>59986.817279495801</v>
       </c>
       <c r="DE36" s="70">
         <f t="shared" si="64"/>
-        <v>51638.129093427582</v>
+        <v>60886.619538688232</v>
       </c>
       <c r="DF36" s="70">
         <f t="shared" si="64"/>
-        <v>52412.70102982899</v>
+        <v>61799.918831768548</v>
       </c>
       <c r="DG36" s="70">
         <f t="shared" si="64"/>
-        <v>53198.891545276419</v>
+        <v>62726.917614245067</v>
       </c>
       <c r="DH36" s="70">
         <f t="shared" si="64"/>
-        <v>53996.874918455564</v>
+        <v>63667.821378458735</v>
       </c>
       <c r="DI36" s="70">
         <f t="shared" si="64"/>
-        <v>54806.828042232395</v>
+        <v>64622.838699135609</v>
       </c>
       <c r="DJ36" s="70">
         <f t="shared" si="64"/>
-        <v>55628.930462865879</v>
+        <v>65592.181279622644</v>
       </c>
       <c r="DK36" s="70">
         <f t="shared" si="64"/>
-        <v>56463.364419808859</v>
+        <v>66576.063998816971</v>
       </c>
       <c r="DL36" s="70">
         <f t="shared" si="64"/>
-        <v>57310.314886105989</v>
+        <v>67574.704958799222</v>
       </c>
       <c r="DM36" s="70">
         <f t="shared" si="64"/>
-        <v>58169.969609397573</v>
+        <v>68588.325533181211</v>
       </c>
       <c r="DN36" s="70">
         <f t="shared" si="64"/>
-        <v>59042.519153538531</v>
+        <v>69617.15041617892</v>
       </c>
       <c r="DO36" s="70">
         <f t="shared" si="64"/>
-        <v>59928.156940841604</v>
+        <v>70661.407672421599</v>
       </c>
       <c r="DP36" s="70">
         <f t="shared" si="64"/>
-        <v>60827.079294954223</v>
+        <v>71721.328787507911</v>
       </c>
       <c r="DQ36" s="70">
         <f t="shared" si="64"/>
-        <v>61739.485484378529</v>
+        <v>72797.148719320525</v>
       </c>
       <c r="DR36" s="70">
         <f t="shared" si="64"/>
-        <v>62665.577766644201</v>
+        <v>73889.10595011033</v>
       </c>
       <c r="DS36" s="70">
         <f t="shared" si="64"/>
-        <v>63605.561433143856</v>
+        <v>74997.442539361975</v>
       </c>
       <c r="DT36" s="70">
         <f t="shared" si="64"/>
-        <v>64559.64485464101</v>
+        <v>76122.404177452394</v>
       </c>
       <c r="DU36" s="70">
         <f t="shared" si="64"/>
-        <v>65528.03952746062</v>
+        <v>77264.240240114174</v>
       </c>
       <c r="DV36" s="70">
         <f t="shared" si="64"/>
-        <v>66510.960120372518</v>
+        <v>78423.203843715877</v>
       </c>
       <c r="DW36" s="70">
         <f t="shared" si="64"/>
-        <v>67508.624522178099</v>
+        <v>79599.551901371611</v>
       </c>
       <c r="DX36" s="70">
         <f t="shared" si="64"/>
-        <v>68521.253890010761</v>
+        <v>80793.545179892171</v>
       </c>
       <c r="DY36" s="70">
         <f t="shared" si="64"/>
-        <v>69549.07269836092</v>
+        <v>82005.448357590547</v>
       </c>
       <c r="DZ36" s="70">
         <f t="shared" si="64"/>
-        <v>70592.308788836322</v>
+        <v>83235.530082954399</v>
       </c>
       <c r="EA36" s="70">
         <f t="shared" si="64"/>
-        <v>71651.19342066886</v>
+        <v>84484.063034198713</v>
       </c>
       <c r="EB36" s="70">
         <f t="shared" ref="EB36:ES36" si="65">EA36*(1+$CU$50)</f>
-        <v>72725.961321978888</v>
+        <v>85751.323979711684</v>
       </c>
       <c r="EC36" s="70">
         <f t="shared" si="65"/>
-        <v>73816.850741808565</v>
+        <v>87037.593839407346</v>
       </c>
       <c r="ED36" s="70">
         <f t="shared" si="65"/>
-        <v>74924.103502935686</v>
+        <v>88343.157746998448</v>
       </c>
       <c r="EE36" s="70">
         <f t="shared" si="65"/>
-        <v>76047.965055479712</v>
+        <v>89668.305113203416</v>
       </c>
       <c r="EF36" s="70">
         <f t="shared" si="65"/>
-        <v>77188.684531311897</v>
+        <v>91013.329689901453</v>
       </c>
       <c r="EG36" s="70">
         <f t="shared" si="65"/>
-        <v>78346.514799281562</v>
+        <v>92378.529635249972</v>
       </c>
       <c r="EH36" s="70">
         <f t="shared" si="65"/>
-        <v>79521.712521270776</v>
+        <v>93764.207579778711</v>
       </c>
       <c r="EI36" s="70">
         <f t="shared" si="65"/>
-        <v>80714.538209089835</v>
+        <v>95170.670693475389</v>
       </c>
       <c r="EJ36" s="70">
         <f t="shared" si="65"/>
-        <v>81925.256282226168</v>
+        <v>96598.230753877506</v>
       </c>
       <c r="EK36" s="70">
         <f t="shared" si="65"/>
-        <v>83154.135126459558</v>
+        <v>98047.204215185659</v>
       </c>
       <c r="EL36" s="70">
         <f t="shared" si="65"/>
-        <v>84401.44715335645</v>
+        <v>99517.912278413438</v>
       </c>
       <c r="EM36" s="70">
         <f t="shared" si="65"/>
-        <v>85667.468860656794</v>
+        <v>101010.68096258963</v>
       </c>
       <c r="EN36" s="70">
         <f t="shared" si="65"/>
-        <v>86952.480893566637</v>
+        <v>102525.84117702846</v>
       </c>
       <c r="EO36" s="70">
         <f t="shared" si="65"/>
-        <v>88256.768106970121</v>
+        <v>104063.72879468388</v>
       </c>
       <c r="EP36" s="70">
         <f t="shared" si="65"/>
-        <v>89580.61962857467</v>
+        <v>105624.68472660413</v>
       </c>
       <c r="EQ36" s="70">
         <f t="shared" si="65"/>
-        <v>90924.328923003282</v>
+        <v>107209.05499750318</v>
       </c>
       <c r="ER36" s="70">
         <f t="shared" si="65"/>
-        <v>92288.193856848316</v>
+        <v>108817.19082246571</v>
       </c>
       <c r="ES36" s="70">
         <f t="shared" si="65"/>
-        <v>93672.516764701038</v>
+        <v>110449.44868480269</v>
       </c>
       <c r="ET36" s="56"/>
       <c r="EU36" s="56"/>
@@ -32666,39 +32663,39 @@
       </c>
       <c r="CM43" s="71">
         <f t="shared" ref="CM43:CU43" si="78">CM29/CM22</f>
-        <v>0.1349284343994023</v>
+        <v>0.13700970728231707</v>
       </c>
       <c r="CN43" s="71">
         <f t="shared" si="78"/>
-        <v>0.15886478439217663</v>
+        <v>0.1608148122081795</v>
       </c>
       <c r="CO43" s="71">
         <f t="shared" si="78"/>
-        <v>0.17707373088101133</v>
+        <v>0.1789083598014258</v>
       </c>
       <c r="CP43" s="71">
         <f t="shared" si="78"/>
-        <v>0.1945385224327662</v>
+        <v>0.19628520671577221</v>
       </c>
       <c r="CQ43" s="71">
         <f t="shared" si="78"/>
-        <v>0.20890266857729689</v>
+        <v>0.21058773564163588</v>
       </c>
       <c r="CR43" s="71">
         <f t="shared" si="78"/>
-        <v>0.22284891231758827</v>
+        <v>0.22448921699741051</v>
       </c>
       <c r="CS43" s="71">
         <f t="shared" si="78"/>
-        <v>0.23635066487084952</v>
+        <v>0.23797405547594427</v>
       </c>
       <c r="CT43" s="71">
         <f t="shared" si="78"/>
-        <v>0.24948193469259927</v>
+        <v>0.25111417736289171</v>
       </c>
       <c r="CU43" s="71">
         <f t="shared" si="78"/>
-        <v>0.25482885235674507</v>
+        <v>0.2564937979178345</v>
       </c>
     </row>
     <row r="44" spans="2:151">
@@ -33366,43 +33363,43 @@
       </c>
       <c r="CL45" s="71">
         <f>CL36/CL22</f>
-        <v>0.10033537594154945</v>
+        <v>0.10163881035800038</v>
       </c>
       <c r="CM45" s="71">
         <f t="shared" ref="CM45:CU45" si="86">CM36/CM22</f>
-        <v>0.13973040899828018</v>
+        <v>0.14226579675410078</v>
       </c>
       <c r="CN45" s="71">
         <f t="shared" si="86"/>
-        <v>0.16656632126997228</v>
+        <v>0.17016337958761882</v>
       </c>
       <c r="CO45" s="71">
         <f t="shared" si="86"/>
-        <v>0.19257467372569825</v>
+        <v>0.19740017269379098</v>
       </c>
       <c r="CP45" s="71">
         <f t="shared" si="86"/>
-        <v>0.21935609754533081</v>
+        <v>0.22558364062219072</v>
       </c>
       <c r="CQ45" s="71">
         <f t="shared" si="86"/>
-        <v>0.24515758573892424</v>
+        <v>0.25301557618577286</v>
       </c>
       <c r="CR45" s="71">
         <f t="shared" si="86"/>
-        <v>0.27223307957440052</v>
+        <v>0.28196454272937493</v>
       </c>
       <c r="CS45" s="71">
         <f t="shared" si="86"/>
-        <v>0.30149762922158369</v>
+        <v>0.31347707847903916</v>
       </c>
       <c r="CT45" s="71">
         <f t="shared" si="86"/>
-        <v>0.33364892609619357</v>
+        <v>0.34836684764790127</v>
       </c>
       <c r="CU45" s="71">
         <f t="shared" si="86"/>
-        <v>0.36261317009198796</v>
+        <v>0.38063589908144885</v>
       </c>
     </row>
     <row r="47" spans="2:151" ht="15" customHeight="1">
@@ -33491,43 +33488,43 @@
       </c>
       <c r="CL47" s="69">
         <f>CK47+CL36</f>
-        <v>7248.7350200000001</v>
+        <v>7293.705645</v>
       </c>
       <c r="CM47" s="53">
         <f t="shared" ref="CM47:CU47" si="92">CL47+CM36</f>
-        <v>13103.445668464999</v>
+        <v>13697.886755864998</v>
       </c>
       <c r="CN47" s="53">
         <f t="shared" si="92"/>
-        <v>21535.258374621077</v>
+        <v>23006.317731561554</v>
       </c>
       <c r="CO47" s="53">
         <f t="shared" si="92"/>
-        <v>33203.755617571296</v>
+        <v>36007.603895930915</v>
       </c>
       <c r="CP47" s="53">
         <f t="shared" si="92"/>
-        <v>48840.673723755041</v>
+        <v>53589.309720388686</v>
       </c>
       <c r="CQ47" s="53">
         <f t="shared" si="92"/>
-        <v>69030.028818237042</v>
+        <v>76501.849974161101</v>
       </c>
       <c r="CR47" s="53">
         <f t="shared" si="92"/>
-        <v>94555.059295157102</v>
+        <v>105735.14821263474</v>
       </c>
       <c r="CS47" s="53">
         <f t="shared" si="92"/>
-        <v>126078.64374849654</v>
+        <v>142174.25719233049</v>
       </c>
       <c r="CT47" s="53">
         <f t="shared" si="92"/>
-        <v>164198.19634041149</v>
+        <v>186653.85416925509</v>
       </c>
       <c r="CU47" s="53">
         <f t="shared" si="92"/>
-        <v>208693.08008765802</v>
+        <v>239117.85907607846</v>
       </c>
     </row>
     <row r="48" spans="2:151" ht="15" customHeight="1">
@@ -33716,7 +33713,7 @@
         <v>1498</v>
       </c>
       <c r="CU49" s="61">
-        <v>0.11749999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="CV49" s="57"/>
     </row>
@@ -33934,7 +33931,7 @@
         <v>1501</v>
       </c>
       <c r="CU51" s="61">
-        <v>4.1459999999999997E-2</v>
+        <v>4.1599999999999998E-2</v>
       </c>
       <c r="CV51" s="57"/>
     </row>
@@ -34050,7 +34047,7 @@
       </c>
       <c r="CU52" s="61">
         <f>7.35%-CU51</f>
-        <v>3.2039999999999999E-2</v>
+        <v>3.1899999999999998E-2</v>
       </c>
       <c r="CV52" s="57"/>
     </row>
@@ -34249,7 +34246,7 @@
       </c>
       <c r="CU54" s="61">
         <f>+CU51+(CU52*CU53)</f>
-        <v>0.10650119999999999</v>
+        <v>0.10635699999999999</v>
       </c>
       <c r="CV54" s="57"/>
     </row>
@@ -34444,7 +34441,7 @@
       </c>
       <c r="CU56" s="62">
         <f>NPV(CU54,CL36:ES36)</f>
-        <v>277455.60887060373</v>
+        <v>323993.03792373196</v>
       </c>
       <c r="CV56" s="57"/>
     </row>
@@ -34659,7 +34656,7 @@
       </c>
       <c r="CU58" s="66">
         <f>CU56/CU57</f>
-        <v>170.63690582447953</v>
+        <v>199.25771090020416</v>
       </c>
       <c r="CV58" s="58"/>
     </row>
@@ -34785,7 +34782,7 @@
       </c>
       <c r="CU59" s="66">
         <f>Main!C3</f>
-        <v>215.08</v>
+        <v>200.54</v>
       </c>
       <c r="CV59" s="68" t="s">
         <v>1780</v>
@@ -34854,7 +34851,7 @@
       </c>
       <c r="CU60" s="61">
         <f>CU58/CU59-1</f>
-        <v>-0.20663517842440249</v>
+        <v>-6.3941812097129125E-3</v>
       </c>
       <c r="CV60" s="58" t="str">
         <f>IF(CU60&gt;0,"Upside","Downside")</f>
@@ -34961,7 +34958,7 @@
       </c>
       <c r="CT61" s="82" t="str" cm="1">
         <f t="array" ref="CT61">_xlfn.IFS(CU60&gt;=25%,"Strong Buy",CU60&gt;=10.00001%,"Buy",AND(CU60&lt;=10%,CU60&gt;=-4.9999%),"Hold",AND(CU60&lt;=-5%,CU60&gt;=-14.999999%),"Sell",CU60&lt;=-15%,"Strong Sell")</f>
-        <v>Strong Sell</v>
+        <v>Hold</v>
       </c>
       <c r="CU61" s="82"/>
     </row>
